--- a/artfynd/A 31328-2022 artfynd.xlsx
+++ b/artfynd/A 31328-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31328-2022 artfynd.xlsx
+++ b/artfynd/A 31328-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103602858</v>
+        <v>103600884</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>369279.6530288139</v>
+        <v>369068</v>
       </c>
       <c r="R2" t="n">
-        <v>6940985.352954971</v>
+        <v>6940926</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103602961</v>
+        <v>103602271</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>369313.0977786315</v>
+        <v>369106</v>
       </c>
       <c r="R3" t="n">
-        <v>6940942.969598491</v>
+        <v>6941134</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103602786</v>
+        <v>103602402</v>
       </c>
       <c r="B4" t="n">
-        <v>79440</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229436</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>369268.5991354898</v>
+        <v>369112</v>
       </c>
       <c r="R4" t="n">
-        <v>6940986.25038029</v>
+        <v>6941099</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103603879</v>
+        <v>103602465</v>
       </c>
       <c r="B5" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +980,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>369155.4683821553</v>
+        <v>369150</v>
       </c>
       <c r="R5" t="n">
-        <v>6940754.010979996</v>
+        <v>6941094</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,12 +1070,7 @@
         <v>103600859</v>
       </c>
       <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>369074.6278615497</v>
+        <v>369075</v>
       </c>
       <c r="R6" t="n">
-        <v>6940906.702851506</v>
+        <v>6940907</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103600680</v>
+        <v>103601892</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>369087.8913477267</v>
+        <v>369035</v>
       </c>
       <c r="R7" t="n">
-        <v>6940716.073554666</v>
+        <v>6941076</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,19 +1234,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103603866</v>
+        <v>103602045</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>369146.2343772622</v>
+        <v>369084</v>
       </c>
       <c r="R8" t="n">
-        <v>6940765.911211875</v>
+        <v>6941085</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,19 +1332,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103601892</v>
+        <v>103602684</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>369035.5812782543</v>
+        <v>369252</v>
       </c>
       <c r="R9" t="n">
-        <v>6941076.193888908</v>
+        <v>6941037</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,19 +1430,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,15 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103602271</v>
+        <v>103602757</v>
       </c>
       <c r="B10" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1470,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>369105.7977177925</v>
+        <v>369257</v>
       </c>
       <c r="R10" t="n">
-        <v>6941134.321898947</v>
+        <v>6941015</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1528,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,15 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103603155</v>
+        <v>103602961</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>369224.3683647143</v>
+        <v>369313</v>
       </c>
       <c r="R11" t="n">
-        <v>6940860.648134577</v>
+        <v>6940943</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1766,19 +1626,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,15 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103601127</v>
+        <v>103603168</v>
       </c>
       <c r="B12" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>369067.01293727</v>
+        <v>369224</v>
       </c>
       <c r="R12" t="n">
-        <v>6941029.735892409</v>
+        <v>6940861</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,19 +1724,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,15 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103602257</v>
+        <v>103603353</v>
       </c>
       <c r="B13" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,21 +1764,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>369110.8111599203</v>
+        <v>369228</v>
       </c>
       <c r="R13" t="n">
-        <v>6941144.274129203</v>
+        <v>6940830</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,19 +1822,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,15 +1851,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103602664</v>
+        <v>103604449</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2047,21 +1862,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>369223.3563157706</v>
+        <v>369028</v>
       </c>
       <c r="R14" t="n">
-        <v>6941010.643669192</v>
+        <v>6940813</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2105,19 +1920,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,15 +1949,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103602087</v>
+        <v>103601127</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,21 +1960,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>369059.3083965373</v>
+        <v>369067</v>
       </c>
       <c r="R15" t="n">
-        <v>6941115.396513162</v>
+        <v>6941030</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2218,19 +2018,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,37 +2047,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103601045</v>
+        <v>103600680</v>
       </c>
       <c r="B16" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>369047.5892523124</v>
+        <v>369088</v>
       </c>
       <c r="R16" t="n">
-        <v>6940982.518360668</v>
+        <v>6940716</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2331,19 +2116,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,37 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103602402</v>
+        <v>103601071</v>
       </c>
       <c r="B17" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2411,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>369112.2573052553</v>
+        <v>369067</v>
       </c>
       <c r="R17" t="n">
-        <v>6941099.002014052</v>
+        <v>6941030</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2444,19 +2214,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,37 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103601010</v>
+        <v>103603866</v>
       </c>
       <c r="B18" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2524,10 +2279,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>369038.2719614648</v>
+        <v>369147</v>
       </c>
       <c r="R18" t="n">
-        <v>6940945.513122803</v>
+        <v>6940765</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,19 +2312,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,15 +2341,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103601066</v>
+        <v>103602858</v>
       </c>
       <c r="B19" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,21 +2352,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2637,10 +2377,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>369060.9974427841</v>
+        <v>369280</v>
       </c>
       <c r="R19" t="n">
-        <v>6941029.512173599</v>
+        <v>6940985</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2670,19 +2410,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,15 +2439,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103603353</v>
+        <v>103600943</v>
       </c>
       <c r="B20" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,21 +2450,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2750,10 +2475,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>369228.7048679602</v>
+        <v>369068</v>
       </c>
       <c r="R20" t="n">
-        <v>6940830.023680427</v>
+        <v>6940926</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2783,19 +2508,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,15 +2537,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103603168</v>
+        <v>103601010</v>
       </c>
       <c r="B21" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,21 +2548,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2863,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>369224.3683647143</v>
+        <v>369038</v>
       </c>
       <c r="R21" t="n">
-        <v>6940860.648134577</v>
+        <v>6940946</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2896,19 +2606,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,15 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103602276</v>
+        <v>103601045</v>
       </c>
       <c r="B22" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2976,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>369105.7977177925</v>
+        <v>369048</v>
       </c>
       <c r="R22" t="n">
-        <v>6941134.321898947</v>
+        <v>6940983</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3009,19 +2704,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,15 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103600876</v>
+        <v>103601066</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3089,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>369078.4214617326</v>
+        <v>369061</v>
       </c>
       <c r="R23" t="n">
-        <v>6940920.856595115</v>
+        <v>6941030</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,19 +2802,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,15 +2831,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103600976</v>
+        <v>103602257</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3177,21 +2842,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3202,10 +2867,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>369044.7859163361</v>
+        <v>369110</v>
       </c>
       <c r="R24" t="n">
-        <v>6940911.573150637</v>
+        <v>6941144</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3235,19 +2900,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3274,15 +2929,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103602684</v>
+        <v>103603879</v>
       </c>
       <c r="B25" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,21 +2940,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3315,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>369252.1267813697</v>
+        <v>369156</v>
       </c>
       <c r="R25" t="n">
-        <v>6941037.191826981</v>
+        <v>6940754</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3348,19 +2998,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3387,15 +3027,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103602757</v>
+        <v>103602087</v>
       </c>
       <c r="B26" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,21 +3038,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3428,10 +3063,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>369257.2516962603</v>
+        <v>369059</v>
       </c>
       <c r="R26" t="n">
-        <v>6941014.842966664</v>
+        <v>6941116</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3461,19 +3096,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,15 +3125,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103600884</v>
+        <v>103600611</v>
       </c>
       <c r="B27" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3516,35 +3136,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>369067.5675790063</v>
+        <v>369065</v>
       </c>
       <c r="R27" t="n">
-        <v>6940926.822249142</v>
+        <v>6940686</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3574,19 +3199,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,15 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103600943</v>
+        <v>103600730</v>
       </c>
       <c r="B28" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,35 +3239,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>369067.5675790063</v>
+        <v>369130</v>
       </c>
       <c r="R28" t="n">
-        <v>6940926.822249142</v>
+        <v>6940846</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3687,19 +3302,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,15 +3331,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103601071</v>
+        <v>103601058</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3742,35 +3342,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>369067.01293727</v>
+        <v>369061</v>
       </c>
       <c r="R29" t="n">
-        <v>6941029.735892409</v>
+        <v>6941007</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3800,19 +3405,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3839,15 +3434,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103601077</v>
+        <v>103601076</v>
       </c>
       <c r="B30" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,35 +3445,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>369067.01293727</v>
+        <v>369067</v>
       </c>
       <c r="R30" t="n">
-        <v>6941029.735892409</v>
+        <v>6941030</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3913,19 +3508,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,15 +3537,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103602465</v>
+        <v>103602363</v>
       </c>
       <c r="B31" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,35 +3548,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>369150.4014018157</v>
+        <v>369117</v>
       </c>
       <c r="R31" t="n">
-        <v>6941093.804631907</v>
+        <v>6941126</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4026,19 +3611,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,15 +3640,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103602045</v>
+        <v>103602739</v>
       </c>
       <c r="B32" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4081,35 +3651,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>369084.4388521948</v>
+        <v>369263</v>
       </c>
       <c r="R32" t="n">
-        <v>6941084.875259362</v>
+        <v>6941037</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4139,19 +3714,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4181,12 +3746,7 @@
         <v>103603370</v>
       </c>
       <c r="B33" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4224,10 +3784,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>369236.7730104892</v>
+        <v>369236</v>
       </c>
       <c r="R33" t="n">
-        <v>6940823.706925644</v>
+        <v>6940824</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4257,19 +3817,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4296,15 +3846,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103600637</v>
+        <v>103603568</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4342,10 +3887,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>369064.5077711135</v>
+        <v>369246</v>
       </c>
       <c r="R34" t="n">
-        <v>6940685.619578574</v>
+        <v>6940818</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4375,19 +3920,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4414,15 +3949,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103602363</v>
+        <v>103603921</v>
       </c>
       <c r="B35" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4460,10 +3990,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>369116.9849250321</v>
+        <v>369148</v>
       </c>
       <c r="R35" t="n">
-        <v>6941125.113884039</v>
+        <v>6940738</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4493,19 +4023,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4532,44 +4052,39 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103603921</v>
+        <v>103600601</v>
       </c>
       <c r="B36" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4578,10 +4093,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>369147.8930511149</v>
+        <v>369065</v>
       </c>
       <c r="R36" t="n">
-        <v>6940737.698604719</v>
+        <v>6940686</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4611,19 +4126,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4650,56 +4155,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103603568</v>
+        <v>103601039</v>
       </c>
       <c r="B37" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>369246.7229723301</v>
+        <v>369048</v>
       </c>
       <c r="R37" t="n">
-        <v>6940818.238775532</v>
+        <v>6940983</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4729,19 +4224,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4768,32 +4253,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>103600730</v>
+        <v>103603582</v>
       </c>
       <c r="B38" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4803,21 +4283,16 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>369130.4655145297</v>
+        <v>369246</v>
       </c>
       <c r="R38" t="n">
-        <v>6940846.359633526</v>
+        <v>6940818</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4847,19 +4322,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4886,15 +4351,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>103601058</v>
+        <v>103603574</v>
       </c>
       <c r="B39" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4902,16 +4362,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4921,21 +4381,16 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>369061.5259680441</v>
+        <v>369246</v>
       </c>
       <c r="R39" t="n">
-        <v>6941007.805849145</v>
+        <v>6940818</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4965,19 +4420,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5004,15 +4449,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>103602739</v>
+        <v>103603812</v>
       </c>
       <c r="B40" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5020,16 +4460,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5037,11 +4477,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5050,10 +4494,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>369263.2168495831</v>
+        <v>369209</v>
       </c>
       <c r="R40" t="n">
-        <v>6941037.215692707</v>
+        <v>6940811</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5083,19 +4527,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5122,15 +4556,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>103601076</v>
+        <v>103602786</v>
       </c>
       <c r="B41" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>81332</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5138,40 +4567,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>229436</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>369067.01293727</v>
+        <v>369268</v>
       </c>
       <c r="R41" t="n">
-        <v>6941029.735892409</v>
+        <v>6940986</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5201,19 +4625,9 @@
           <t>2022-09-17</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 31328-2022 artfynd.xlsx
+++ b/artfynd/A 31328-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103600884</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602271</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602402</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602465</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103600859</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103601892</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602045</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602684</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602757</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602961</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603168</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603353</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103604449</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103601127</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103600680</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2240,6 +2320,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103601071</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2338,6 +2423,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603866</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602858</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2534,6 +2629,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103600943</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103601010</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2730,6 +2835,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103601045</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103601066</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2926,6 +3041,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602257</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3024,6 +3144,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603879</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602087</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3225,6 +3355,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103600611</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3328,6 +3463,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103600730</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3431,6 +3571,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103601058</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3534,6 +3679,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103601076</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3637,6 +3787,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602363</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3740,6 +3895,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602739</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3843,6 +4003,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603370</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3946,6 +4111,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603568</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4049,6 +4219,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603921</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4152,6 +4327,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103600601</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4250,6 +4430,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103601039</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4348,6 +4533,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603582</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4446,6 +4636,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603574</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4553,6 +4748,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103603812</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4651,8 +4851,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103602786</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>